--- a/survey_templates/040_smart_goals_assessment--survey_templates.xlsx
+++ b/survey_templates/040_smart_goals_assessment--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -440,10 +440,10 @@
   <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,7 +520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>survey_templates_1</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -528,7 +528,11 @@
           <t>Introduction</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>This form will help you assess the SMARTness of a goal.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -543,7 +547,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>question_1</t>
+          <t>goal_clarity</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -551,10 +555,14 @@
           <t>Is the goal clear?</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Describe the goal in one sentence.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,7 +574,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>question_2</t>
+          <t>goal_achievable</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -574,22 +582,26 @@
           <t>Is the goal achievable?</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Consider the resources and challenges.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>question_3</t>
+          <t>goal_relevance</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -597,10 +609,14 @@
           <t>Is the goal relevant?</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>How does it align with your overall objectives?</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,18 +628,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>question_4</t>
+          <t>goal_measurability</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Is the goal measurable?</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>How will you measure progress towards the goal?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Provide specific metrics or indicators.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,7 +655,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>question_5</t>
+          <t>goal_attainability</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -643,22 +663,26 @@
           <t>Is the goal attainable?</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Consider the resources and challenges.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>question_6</t>
+          <t>goal_timeliness</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -666,10 +690,14 @@
           <t>Is the goal time-bound?</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Provide a specific deadline or timeframe.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,7 +709,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>question_7</t>
+          <t>goal_specificty</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -689,10 +717,14 @@
           <t>Is the goal specific?</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Clearly define what needs to be achieved.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,18 +736,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>question_8</t>
+          <t>goal_outcome</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Is the goal measurable?</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>What is the expected outcome or result of achieving the goal?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Describe the benefits or impact.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,18 +763,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>question_9</t>
+          <t>goal_progress_tracking</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Is the goal measurable?</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>How will you track and report progress towards the goal?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Describe your process.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,38 +790,46 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>question_10</t>
+          <t>goal_impact</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Is the goal measurable?</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>What is the expected impact or benefit of achieving the goal?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Describe the effects on your work or life.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>question_11</t>
+          <t>introduction_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Is the goal measurable?</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Additional comments or feedback.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Please share any additional thoughts or insights.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -802,9 +850,9 @@
   <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -827,170 +875,170 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>goal_achievable_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>goal_achievable_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>goal_relevance_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'goal_is_relevant'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Goal is relevant'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>goal_relevance_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'goal_is_irrelevant'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Goal is irrelevant'}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>goal_attainability_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>goal_attainability_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>question_6_choices</t>
+          <t>goal_timeliness_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'time-bound'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Time-bound'}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>question_6_choices</t>
+          <t>goal_timeliness_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'not_time-bound'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Not time-bound'}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>question_7_choices</t>
+          <t>goal_specificty_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>question_7_choices</t>
+          <t>goal_specificty_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
